--- a/Capítulo04/HOTEL.xlsx
+++ b/Capítulo04/HOTEL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\Publica\PROF RAUL\_2024 EXCEL FORMAÇÃO 08-01-2024\_AVANÇADO 1 e 2\Capítulo04\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://senacspedu-my.sharepoint.com/personal/yuri_smendes_senacsp_edu_br/Documents/Capítulo04/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F29B719-0D6C-4566-8F47-A74D6517DD95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{8F29B719-0D6C-4566-8F47-A74D6517DD95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C26B7E44-799A-4FB0-9D01-B823F2F32C1F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ORIGINAL" sheetId="1" r:id="rId1"/>
@@ -271,10 +271,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -605,17 +605,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
     </row>
     <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
@@ -870,17 +870,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E2" s="1"/>
@@ -1306,6 +1306,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100CEB2B541769F8A4991DE642272C524BB" ma:contentTypeVersion="0" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="7ae862ae5010eca0394e8ac9f072291e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="397561fba88d9dece65508bac662637b">
     <xsd:element name="properties">
@@ -1419,23 +1434,13 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5894E504-1C78-4C11-A2BC-097F0BBB7355}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89DB20E4-C695-4F37-AD43-56D310C16F20}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1447,9 +1452,16 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89DB20E4-C695-4F37-AD43-56D310C16F20}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5894E504-1C78-4C11-A2BC-097F0BBB7355}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
